--- a/series_data/planetfall/series_log.xlsx
+++ b/series_data/planetfall/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -704,6 +704,226 @@
       <c r="M5" t="inlineStr">
         <is>
           <t>/home/runner/work/youtube-automation/youtube-automation/output/series/planetfall/episodes/ep01/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-07-04 17:38</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/e3201ee2470495d90b52e5da88f13930_1783186687.mp4</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/planetfall/episodes/ep02/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-07-04 17:48</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/vw/2f2d20d8ef8de3ab639aa8c4de34eaa6.mp4</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/planetfall/episodes/ep02/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-07-04 17:53</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/vw/54e670986e9144c995482d1cdb9d865a.mp4</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/planetfall/episodes/ep02/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-07-04 17:57</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/a1678c79df98f063749b6db8a95a7f14_1783187814.mp4</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/planetfall/episodes/ep02/shots/shot_04.mp4</t>
         </is>
       </c>
     </row>

--- a/series_data/planetfall/series_log.xlsx
+++ b/series_data/planetfall/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -927,6 +927,226 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-07-05 17:42</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/229e1bbef063875d7d83d7659a9f8b81_1783273301.mp4</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/planetfall/episodes/ep03/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-07-05 17:49</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/e0b31d170876b612a591f926a4321a74_1783273740.mp4</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/planetfall/episodes/ep03/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-07-05 17:52</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/45707f2bc0bde02c9081f0f2bda9a622_1783273887.mp4</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/planetfall/episodes/ep03/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-07-05 17:56</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/093d4fdc440bc1386ca6dcb4238461ee_1783274167.mp4</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/planetfall/episodes/ep03/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/series_data/planetfall/series_log.xlsx
+++ b/series_data/planetfall/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M13"/>
+  <dimension ref="A1:M17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1147,6 +1147,226 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-07-06 18:31</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/3f5ce7d81438fae34743938874cae211_1783362631.mp4</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/planetfall/episodes/ep04/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-07-06 18:34</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/ec2f65781753e4ec03e55ab84e159b4c_1783362847.mp4</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/planetfall/episodes/ep04/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-07-06 18:38</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/3c933d0b76e8e9156bb3eaa3b87599eb_1783363074.mp4</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/planetfall/episodes/ep04/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-07-06 18:41</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/c38be2141cfa713d8b4978112e9a4b4f_1783363279.mp4</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/planetfall/episodes/ep04/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/series_data/planetfall/series_log.xlsx
+++ b/series_data/planetfall/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M17"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1367,6 +1367,226 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-07-07 18:35</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/cac59a756d6fa5bd7be0531acb3c54df_1783449315.mp4</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/planetfall/episodes/ep05/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-07-07 18:38</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/1aee61e4afe9806054746b012f41b916_1783449498.mp4</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/planetfall/episodes/ep05/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-07-07 18:44</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/76b471e346cd2e075d0cad41508431a9_1783449847.mp4</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/planetfall/episodes/ep05/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-07-07 18:49</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/23b97b4b0e51927a3a9e10e548d2c506_1783450119.mp4</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/planetfall/episodes/ep05/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/series_data/planetfall/series_log.xlsx
+++ b/series_data/planetfall/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1587,6 +1587,226 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-07-08 18:04</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/e3d24e8fc14dc0735c757eeec1d88e76_1783533826.mp4</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/planetfall/episodes/ep06/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-07-08 18:07</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/11033a0f944d200eaffcdbeeb260748e_1783534029.mp4</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/planetfall/episodes/ep06/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-07-08 18:11</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/b93be9692f734dcef1baa0f546e977ec_1783534277.mp4</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/planetfall/episodes/ep06/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-07-08 18:14</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/f58bb1dfc3d5ece6a8d96078c3a2044b_1783534452.mp4</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/planetfall/episodes/ep06/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/series_data/planetfall/series_log.xlsx
+++ b/series_data/planetfall/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M25"/>
+  <dimension ref="A1:M29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1807,6 +1807,226 @@
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-07-09 18:20</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/faf67c14f305ec6a3c9b44e926cdf5c3_1783621220.mp4</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/planetfall/episodes/ep07/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-07-09 18:23</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/e1788291729560ec70e3721bf3edecfc_1783621376.mp4</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/planetfall/episodes/ep07/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-07-09 18:28</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/76952f1c3bf294c4c37ed77fec5a7aaa_1783621704.mp4</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/planetfall/episodes/ep07/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-07-09 18:31</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/6ddf6545ae4631931c71fb3a3b09b06b_1783621839.mp4</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/planetfall/episodes/ep07/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/series_data/planetfall/series_log.xlsx
+++ b/series_data/planetfall/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M29"/>
+  <dimension ref="A1:M33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2027,6 +2027,226 @@
         </is>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-07-10 18:15</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/7cf65225ed59456144e6ae88773e6bd5_1783707296.mp4</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/planetfall/episodes/ep08/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-07-10 18:18</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/0ff08d6066060b2fae56390115f69ac9_1783707481.mp4</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/planetfall/episodes/ep08/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-07-10 18:20</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/b69e7ac82a75b9761d9902b217bb41ef_1783707623.mp4</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/planetfall/episodes/ep08/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-07-10 18:23</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/bd7b7b4d9422062b14d1a9d1998a95d6_1783707762.mp4</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/planetfall/episodes/ep08/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/series_data/planetfall/series_log.xlsx
+++ b/series_data/planetfall/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M33"/>
+  <dimension ref="A1:M37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2247,6 +2247,226 @@
         </is>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-07-11 17:33</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/8d36eedf066836fb2da315802eb2abc8_1783791157.mp4</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/planetfall/episodes/ep09/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-07-11 17:35</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/2e1a5db25ad97677e8bec2118201470a_1783791304.mp4</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/planetfall/episodes/ep09/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-07-11 17:38</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/a0ccead79efd9cb708c39b7666a1c6e8_1783791451.mp4</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/planetfall/episodes/ep09/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-07-11 17:40</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/fb440ce21f7d6ce8723b3c2ef66a4d52_1783791607.mp4</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/planetfall/episodes/ep09/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/series_data/planetfall/series_log.xlsx
+++ b/series_data/planetfall/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M37"/>
+  <dimension ref="A1:M41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2467,6 +2467,226 @@
         </is>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-07-12 17:36</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/vw/ea5fb1d9500a1077f172654facebfc37.mp4</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/planetfall/episodes/ep10/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-07-12 17:40</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/vw/ab5e23f200ffdc0f8435da9cf3990fcb.mp4</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/planetfall/episodes/ep10/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-07-12 17:43</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/vw/655225c962f32fc72cc97ad403ed9bd3.mp4</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/planetfall/episodes/ep10/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-07-12 17:45</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/f53ce81b8d4e21de2f62bd0d26891af0_1783878315.mp4</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/planetfall/episodes/ep10/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/series_data/planetfall/series_log.xlsx
+++ b/series_data/planetfall/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M41"/>
+  <dimension ref="A1:M45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2687,6 +2687,226 @@
         </is>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-07-13 18:20</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/vw/53464c988d608af21b1c1f73cb5f6b77.mp4</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/planetfall/episodes/ep11/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-07-13 18:24</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/vw/835a70d84f5a2abc45f104f574d62bdb.mp4</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/planetfall/episodes/ep11/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-07-13 18:28</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/vw/786f0de48ab98c73b3e450c98388420a.mp4</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/planetfall/episodes/ep11/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-07-13 18:34</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>210.0</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>1.05</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/vw/61471cb29c9693b808ad78015e6406fc.mp4</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/planetfall/episodes/ep11/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/series_data/planetfall/series_log.xlsx
+++ b/series_data/planetfall/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M45"/>
+  <dimension ref="A1:M49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2907,6 +2907,226 @@
         </is>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-07-14 17:44</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/vw/4038a9be0dc37fe38865e537d5f66ffe.mp4</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/planetfall/episodes/ep12/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-07-14 17:47</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/vw/aa515b127af60309560106e1517f9681.mp4</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/planetfall/episodes/ep12/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-07-14 17:53</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/vw/3509efc32c1cb0b3b8d3c1f6c00788bf.mp4</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/planetfall/episodes/ep12/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-07-14 17:56</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/vw/17a6aa59c4c9ee7b8946de60aead56bd.mp4</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/planetfall/episodes/ep12/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/series_data/planetfall/series_log.xlsx
+++ b/series_data/planetfall/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M49"/>
+  <dimension ref="A1:M53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3127,6 +3127,226 @@
         </is>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-07-15 17:50</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/5c8138752704a57b428d55a386a8cf4b_1784137794.mp4</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/planetfall/episodes/ep13/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-07-15 17:53</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/727ba708264686de06a8f4ffb40ae685_1784137962.mp4</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/planetfall/episodes/ep13/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-07-15 17:56</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/cea1f2248c066cea5663b85ae5bc3d79_1784138147.mp4</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/planetfall/episodes/ep13/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-07-15 18:04</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>315.0</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>1.575</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/b9e20852b158f8224f184c27180a0d67_1784138365.mp4</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/planetfall/episodes/ep13/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/series_data/planetfall/series_log.xlsx
+++ b/series_data/planetfall/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M53"/>
+  <dimension ref="A1:M57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3347,6 +3347,226 @@
         </is>
       </c>
     </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-07-16 17:49</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/19591245fcbacdc6022e04418bc28865_1784224154.mp4</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/planetfall/episodes/ep14/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-07-16 17:57</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>315.0</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>1.575</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/b7509f39eadb2199c3280478c9214a52_1784224321.mp4</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/planetfall/episodes/ep14/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-07-16 18:00</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/4588dad73118c60bb9c294cf6700191d_1784224767.mp4</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/planetfall/episodes/ep14/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-07-16 18:03</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/42c84facdf982538b46817c685df7215_1784224939.mp4</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/planetfall/episodes/ep14/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/series_data/planetfall/series_log.xlsx
+++ b/series_data/planetfall/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M57"/>
+  <dimension ref="A1:M61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3567,6 +3567,226 @@
         </is>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-07-17 17:44</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>210.0</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>1.05</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/af11a88c3a2bfaad2601248e95e6efdf_1784310075.mp4</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/planetfall/episodes/ep15/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-07-17 17:47</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/6c2bc52a8171853a749afa86d9b8dc23_1784310422.mp4</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/planetfall/episodes/ep15/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-07-17 17:50</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/ba7e93e42dab84afeb504add579804eb_1784310608.mp4</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/planetfall/episodes/ep15/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-07-17 17:54</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/85cc63eca576aca0681bec6922962074_1784310815.mp4</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/planetfall/episodes/ep15/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/series_data/planetfall/series_log.xlsx
+++ b/series_data/planetfall/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M61"/>
+  <dimension ref="A1:M65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3787,6 +3787,226 @@
         </is>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-07-18 17:34</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/1ec034e4bfdc29c3666e540e34564052_1784396059.mp4</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/planetfall/episodes/ep16/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-07-18 17:37</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/2ba7ea98f132d778a07906a08e8f4a21_1784396221.mp4</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/planetfall/episodes/ep16/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-07-18 17:42</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>210.0</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>1.05</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/fc870b4156b85f9917c736fcca1a25ee_1784396397.mp4</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/planetfall/episodes/ep16/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-07-18 17:49</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>210.0</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>1.05</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/0cb502d143434cecc922e6b7534278c3_1784396728.mp4</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/planetfall/episodes/ep16/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/series_data/planetfall/series_log.xlsx
+++ b/series_data/planetfall/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M65"/>
+  <dimension ref="A1:M69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4007,6 +4007,226 @@
         </is>
       </c>
     </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-07-19 17:34</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/41a08b32b006bbcda3a8679079219413_1784482434.mp4</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/planetfall/episodes/ep17/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-07-19 17:37</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/280864bf0ff597ea44c64ecb96fbfbec_1784482619.mp4</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/planetfall/episodes/ep17/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-07-19 17:40</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/8b53ad6bbb21d200bcbb55b1ea8680d7_1784482802.mp4</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/planetfall/episodes/ep17/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-07-19 17:43</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/aab2c5d7e2e5764b31ee6a37ff73dd20_1784482990.mp4</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/planetfall/episodes/ep17/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/series_data/planetfall/series_log.xlsx
+++ b/series_data/planetfall/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M69"/>
+  <dimension ref="A1:M73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4227,6 +4227,226 @@
         </is>
       </c>
     </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-07-20 18:32</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/47773e2ef3761c00932659d9f6eb065f_1784572313.mp4</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/planetfall/episodes/ep18/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-07-20 18:35</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/02a1a6a4c9aa3ee020b9e4bba25a5fca_1784572465.mp4</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/planetfall/episodes/ep18/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-07-20 18:37</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/379c5850703b6b62d777ad3a45ef22f4_1784572640.mp4</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/planetfall/episodes/ep18/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-07-20 18:40</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/d2da6873c0bb0f7f16f96a3ffcb6823f_1784572802.mp4</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/planetfall/episodes/ep18/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/series_data/planetfall/series_log.xlsx
+++ b/series_data/planetfall/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M73"/>
+  <dimension ref="A1:M77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4447,6 +4447,226 @@
         </is>
       </c>
     </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-07-21 17:59</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>210.0</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>1.05</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/vw/bd21f1a777d33289c8deac71c7137c8a.mp4</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/planetfall/episodes/ep19/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-07-21 18:02</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/c3964a870094762111866677016e9264_1784656890.mp4</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/planetfall/episodes/ep19/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-07-21 18:04</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/vw/af20050af9778b04584bad028eb1e750.mp4</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/planetfall/episodes/ep19/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-07-21 18:09</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>210.0</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>1.05</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/8f1e294e06e2092476382c0972962da4_1784657226.mp4</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/planetfall/episodes/ep19/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/series_data/planetfall/series_log.xlsx
+++ b/series_data/planetfall/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M77"/>
+  <dimension ref="A1:M81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4667,6 +4667,226 @@
         </is>
       </c>
     </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-07-22 17:51</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/ac7513ee544d1e7436d127a78e490f6f_1784742672.mp4</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/planetfall/episodes/ep20/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-07-22 17:54</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/28d1e74fcccc07ad01bf6bb124735b8c_1784742828.mp4</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/planetfall/episodes/ep20/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-07-22 17:56</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/bd5f4ecf56b7eda03c5559d90d257b15_1784742981.mp4</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/planetfall/episodes/ep20/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-07-22 17:59</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/91d532dea31f0a351397f1088a41129b_1784743148.mp4</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/planetfall/episodes/ep20/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/series_data/planetfall/series_log.xlsx
+++ b/series_data/planetfall/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M81"/>
+  <dimension ref="A1:M85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4887,6 +4887,226 @@
         </is>
       </c>
     </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-07-23 18:06</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>210.0</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>1.05</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/2928172053579b02826bd954d69536b2_1784829635.mp4</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/planetfall/episodes/ep21/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-07-23 18:11</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/b9391d3963602f4d428b15e0f349a9b6_1784830225.mp4</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/planetfall/episodes/ep21/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-07-23 18:15</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr"/>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/9084dbc88111fec7cd2bac3abae38c9c_1784830513.mp4</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/planetfall/episodes/ep21/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-07-23 18:20</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/77ab48f8eec2b239e546c2f724e5bff7_1784830798.mp4</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/planetfall/episodes/ep21/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/series_data/planetfall/series_log.xlsx
+++ b/series_data/planetfall/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M85"/>
+  <dimension ref="A1:M89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5107,6 +5107,226 @@
         </is>
       </c>
     </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-07-24 18:05</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr"/>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>210.0</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>1.05</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/1e434df084fcbf282ba7ddd14b17dc26_1784916113.mp4</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/planetfall/episodes/ep22/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-07-24 18:07</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/cf559886b94b8878cebcf2fd417a2cc2_1784916417.mp4</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/planetfall/episodes/ep22/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-07-24 18:12</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr"/>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>210.0</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>1.05</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/700086f4c1c43360f26791f7e589ab0a_1784916574.mp4</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/planetfall/episodes/ep22/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-07-24 18:15</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr"/>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/59ad6cc366071670220f4b0427f283a4_1784916909.mp4</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/planetfall/episodes/ep22/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/series_data/planetfall/series_log.xlsx
+++ b/series_data/planetfall/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M89"/>
+  <dimension ref="A1:M93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5327,6 +5327,226 @@
         </is>
       </c>
     </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-07-25 17:37</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>210.0</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>1.05</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/vw/86493889f0e1a198eb875bba63e7c094.mp4</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/planetfall/episodes/ep23/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-07-25 17:39</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="inlineStr"/>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/3fe719d7f061d7923a86c7d63d5e92c4_1785001158.mp4</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/planetfall/episodes/ep23/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-07-25 17:43</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="inlineStr"/>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/vw/61e8d1fcb717fdeae49dfc8198690321.mp4</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/planetfall/episodes/ep23/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-07-25 17:47</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr"/>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/vw/4e2adb03fa6008c84bffca2b84a9135e.mp4</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/planetfall/episodes/ep23/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/series_data/planetfall/series_log.xlsx
+++ b/series_data/planetfall/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M93"/>
+  <dimension ref="A1:M97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5547,6 +5547,226 @@
         </is>
       </c>
     </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-07-26 17:36</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="inlineStr"/>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/795a7a35357fa35ee50ea79e72e9a942_1785087328.mp4</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/planetfall/episodes/ep24/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-07-26 17:39</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="inlineStr"/>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/ed4f58e6791ddbd82bfcc50edce6d41e_1785087503.mp4</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/planetfall/episodes/ep24/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-07-26 17:42</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr"/>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/vw/cba1a17df83ca1eda06c7d20424b8448.mp4</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/planetfall/episodes/ep24/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-07-26 17:46</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="inlineStr"/>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/vw/1db15955013d144cda7ccd83d253037a.mp4</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/planetfall/episodes/ep24/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/series_data/planetfall/series_log.xlsx
+++ b/series_data/planetfall/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M97"/>
+  <dimension ref="A1:M101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5767,6 +5767,226 @@
         </is>
       </c>
     </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-07-27 18:12</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="inlineStr"/>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>210.0</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>1.05</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/vw/d2933f77fee464898f36de92c53f3070.mp4</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/planetfall/episodes/ep25/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-07-27 18:15</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr"/>
+      <c r="E99" t="inlineStr"/>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/8c59928ad22cc20d763c405341fdeb84_1785176099.mp4</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/planetfall/episodes/ep25/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-07-27 18:18</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr"/>
+      <c r="E100" t="inlineStr"/>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/ec52dd088170c48c0463ddc9f3b09ee4_1785176266.mp4</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/planetfall/episodes/ep25/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-07-27 18:21</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr"/>
+      <c r="E101" t="inlineStr"/>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/vw/e25351321613077a0e37438fe1765474.mp4</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/planetfall/episodes/ep25/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
